--- a/Result/profitability/8928.xlsx
+++ b/Result/profitability/8928.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3675</v>
+        <v>0.41875</v>
       </c>
       <c r="N2" t="n">
-        <v>12.18875</v>
+        <v>12.39875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.44125</v>
+        <v>0.3375</v>
       </c>
       <c r="N3" t="n">
-        <v>13.095</v>
+        <v>13.48375</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.53</v>
       </c>
       <c r="M4" t="n">
-        <v>0.38375</v>
+        <v>0.21625</v>
       </c>
       <c r="N4" t="n">
-        <v>14.0675</v>
+        <v>13.725</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.19625</v>
+        <v>0.42</v>
       </c>
       <c r="N5" t="n">
-        <v>13.81625</v>
+        <v>13.9275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.45</v>
+        <v>0.43625</v>
       </c>
       <c r="N6" t="n">
-        <v>14.5975</v>
+        <v>15.14</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1266,16 +1266,16 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.41375</v>
+        <v>0.275</v>
       </c>
       <c r="N7" t="n">
-        <v>15.29625</v>
+        <v>15.57</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1393,10 +1393,10 @@
         <v>-0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.225</v>
+        <v>0.1625</v>
       </c>
       <c r="N8" t="n">
-        <v>15.3625</v>
+        <v>15.35875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8928</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>616</v>
+      </c>
+      <c r="D75" t="n">
+        <v>538</v>
+      </c>
+      <c r="E75" t="n">
+        <v>78</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>14</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.20%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7575757575757576</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.03000000000000114</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.002356637863315081</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.098159509202454</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.8899999999999988</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07535986452159182</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
